--- a/important_mails_2026-04-01.xlsx
+++ b/important_mails_2026-04-01.xlsx
@@ -809,7 +809,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -824,73 +824,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
+          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (kpCypnMqWe)</t>
+          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1188095-0289626
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1372192148348110</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -913,39 +861,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -965,39 +913,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -1014,39 +962,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -1066,39 +1014,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1116,39 +1064,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1166,39 +1114,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1216,39 +1164,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -1263,39 +1211,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1313,39 +1261,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1363,39 +1311,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1413,39 +1361,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1460,39 +1408,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1507,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1555,39 +1503,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -1616,39 +1564,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -1669,39 +1617,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1716,39 +1664,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1762,40 +1710,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1811,39 +1759,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1859,39 +1807,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -1907,39 +1855,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -1955,40 +1903,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2004,39 +1952,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2054,39 +2002,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -2102,86 +2050,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 03/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
- 41.37 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pér</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2202,39 +2103,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2257,39 +2158,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -2305,39 +2206,91 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (kpCypnMqWe)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1188095-0289626
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1372192148348110</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2363,39 +2316,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2411,39 +2364,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2464,39 +2417,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2510,40 +2463,40 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2559,39 +2512,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2611,39 +2564,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2657,39 +2610,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2709,39 +2662,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2762,39 +2715,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2814,39 +2767,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2866,39 +2819,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2915,39 +2868,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2962,39 +2915,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3018,39 +2971,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3064,39 +3017,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3113,39 +3066,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3165,39 +3118,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3214,39 +3167,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3270,39 +3223,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -3322,39 +3275,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3369,39 +3322,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3420,40 +3373,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3472,39 +3425,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3514,39 +3467,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3564,39 +3517,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3612,39 +3565,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3663,39 +3616,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3713,39 +3666,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3767,39 +3720,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3822,39 +3775,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3873,39 +3826,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3924,39 +3877,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3976,39 +3929,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -4028,39 +3981,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -4078,39 +4031,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -4128,39 +4081,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -4178,39 +4131,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4226,6 +4179,53 @@
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
  For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
  To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 03/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
+ 41.37 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pér</t>
         </is>
       </c>
     </row>
